--- a/Stats Sheet/Round Gaps/Ad-Libitum.xlsx
+++ b/Stats Sheet/Round Gaps/Ad-Libitum.xlsx
@@ -82,16 +82,16 @@
     <x:t>Kelawesome</x:t>
   </x:si>
   <x:si>
-    <x:t>Kubaslov</x:t>
+    <x:t>MajorWoof</x:t>
+  </x:si>
+  <x:si>
+    <x:t>natsuvi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nikikula</x:t>
   </x:si>
   <x:si>
     <x:t>187</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MajorWoof</x:t>
-  </x:si>
-  <x:si>
-    <x:t>natsuvi</x:t>
   </x:si>
   <x:si>
     <x:t>ohh_lia</x:t>
@@ -952,13 +952,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H17" s="0" t="s">
-        <x:v>23</x:v>
+      <x:c r="F17" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -966,21 +969,15 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -989,16 +986,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
@@ -1084,7 +1084,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I23" s="0" t="s">
         <x:v>6</x:v>
